--- a/ruler_chung/THUOC_TT20_2022_BYT.xlsx
+++ b/ruler_chung/THUOC_TT20_2022_BYT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\check_3176_NEW_13072026\danh_muc_cong\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\CHECK_3176_NEW_UPDATE\ruler_chung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EC4830-1DF2-484C-96C4-D0E67E73F035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECAF650-B0BE-4D89-8100-E34DDB5EEB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>MA_HOAT_CHAT</t>
   </si>
@@ -46,6 +46,18 @@
   </si>
   <si>
     <t>I10</t>
+  </si>
+  <si>
+    <t>40.61</t>
+  </si>
+  <si>
+    <t>Colchicin</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>TT35/TT-BYT; TT50/TT-BYT</t>
   </si>
 </sst>
 </file>
@@ -364,15 +376,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -386,7 +399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -398,6 +411,23 @@
       </c>
       <c r="D2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
